--- a/OUTPUT/reverse_Q8PN77_Xanthomonas_axonopodis_pv__citri_str__306.xlsx
+++ b/OUTPUT/reverse_Q8PN77_Xanthomonas_axonopodis_pv__citri_str__306.xlsx
@@ -482,11 +482,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACATGT</t>
+          <t>TGTACA</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0046</v>
+        <v>0.004798080767692923</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.6868</v>
+        <v>0.6867253098760496</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>ACA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.6868</v>
+        <v>0.6867253098760496</v>
       </c>
     </row>
   </sheetData>
